--- a/metrics/mobile-component-metrics-2026-02-24.xlsx
+++ b/metrics/mobile-component-metrics-2026-02-24.xlsx
@@ -74,7 +74,7 @@
     <t>app/component-library/components/Texts/Text/Text.tsx</t>
   </si>
   <si>
-    <t>22.97%</t>
+    <t>22.94%</t>
   </si>
   <si>
     <t>Icon</t>
@@ -92,6 +92,12 @@
     <t>app/component-library/components/Form/Label/Label.tsx</t>
   </si>
   <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Cards/Card/Card.tsx</t>
+  </si>
+  <si>
     <t>ButtonIcon</t>
   </si>
   <si>
@@ -131,12 +137,6 @@
     <t>14.98%</t>
   </si>
   <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Cards/Card/Card.tsx</t>
-  </si>
-  <si>
     <t>BottomSheetFooter</t>
   </si>
   <si>
@@ -164,6 +164,18 @@
     <t>app/component-library/components/Form/TextField/foundation/Input/Input.tsx</t>
   </si>
   <si>
+    <t>ButtonLink</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Buttons/Button/variants/ButtonLink/ButtonLink.tsx</t>
+  </si>
+  <si>
+    <t>TextButton</t>
+  </si>
+  <si>
+    <t>7.14%</t>
+  </si>
+  <si>
     <t>ButtonBase</t>
   </si>
   <si>
@@ -173,18 +185,6 @@
     <t>20.00%</t>
   </si>
   <si>
-    <t>ButtonLink</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Buttons/Button/variants/ButtonLink/ButtonLink.tsx</t>
-  </si>
-  <si>
-    <t>TextButton</t>
-  </si>
-  <si>
-    <t>7.14%</t>
-  </si>
-  <si>
     <t>BadgeNetwork</t>
   </si>
   <si>
@@ -197,6 +197,15 @@
     <t>app/component-library/components/Avatars/Avatar/foundation/AvatarBase/AvatarBase.tsx</t>
   </si>
   <si>
+    <t>AvatarToken</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarToken/AvatarToken.tsx</t>
+  </si>
+  <si>
+    <t>17.50%</t>
+  </si>
+  <si>
     <t>AvatarNetwork</t>
   </si>
   <si>
@@ -218,15 +227,6 @@
     <t>app/component-library/components/Avatars/Avatar/variants/AvatarFavicon/AvatarFavicon.tsx</t>
   </si>
   <si>
-    <t>AvatarToken</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarToken/AvatarToken.tsx</t>
-  </si>
-  <si>
-    <t>17.50%</t>
-  </si>
-  <si>
     <t>AvatarAccount</t>
   </si>
   <si>
@@ -236,7 +236,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>20.58%</t>
+    <t>20.56%</t>
   </si>
   <si>
     <t>Old Component</t>
@@ -293,7 +293,7 @@
     <t>TabBar</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Nav/Main/MainNavigator.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Nav/Main/MainNavigator.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx</t>
   </si>
   <si>
     <t>SheetActions</t>
@@ -329,13 +329,13 @@
     <t>HeaderStackedStandard</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx</t>
   </si>
   <si>
     <t>HeaderCompactStandard</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
   </si>
   <si>
     <t>ConditionalScrollView</t>
@@ -356,39 +356,39 @@
     <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx, repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx, repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx, repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx</t>
   </si>
   <si>
+    <t>repos/metamask-mobile/app/components/Nav/App/App.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx</t>
+  </si>
+  <si>
+    <t>ToastContextWrapper</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Root/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
+  </si>
+  <si>
+    <t>Overlay</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx</t>
+  </si>
+  <si>
     <t>TagBase</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Earn/components/OutputAmountTag/OutputAmountTag.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Nav/App/App.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx</t>
-  </si>
-  <si>
-    <t>ToastContextWrapper</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Root/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
-  </si>
-  <si>
-    <t>Overlay</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx</t>
-  </si>
-  <si>
     <t>TabsList</t>
   </si>
   <si>
@@ -419,16 +419,22 @@
     <t>repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx</t>
   </si>
   <si>
+    <t>ButtonToggle</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
+  </si>
+  <si>
+    <t>ButtonSemantic</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx</t>
+  </si>
+  <si>
     <t>ButtonPill</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
-  </si>
-  <si>
-    <t>ButtonToggle</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
   </si>
   <si>
     <t>ButtonHero</t>
@@ -437,19 +443,19 @@
     <t>repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
   </si>
   <si>
-    <t>ButtonSemantic</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx</t>
-  </si>
-  <si>
     <t>AccountBalance</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/ApproveTransactionHeader/ApproveTransactionHeader.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+  </si>
+  <si>
+    <t>SensitiveText</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx</t>
   </si>
   <si>
     <t>TagUrl</t>
@@ -458,12 +464,6 @@
     <t>repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/UI/ApprovalTagUrl/ApprovalTagUrl.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
   </si>
   <si>
-    <t>SensitiveText</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx</t>
-  </si>
-  <si>
     <t>Tag</t>
   </si>
   <si>
@@ -473,64 +473,64 @@
     <t>repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingleSelector/AccountConnectSingleSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealPrivateKey/RevealPrivateKey.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
   </si>
   <si>
+    <t>SelectButton</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx</t>
+  </si>
+  <si>
     <t>PickerNetwork</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/PaymentRequest/index.js, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx</t>
   </si>
   <si>
-    <t>SelectButton</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
+    <t>ListItemSelect</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
+  </si>
+  <si>
+    <t>ListItemMultiSelect</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx</t>
+  </si>
+  <si>
+    <t>ListItemColumn</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
+  </si>
+  <si>
+    <t>ListItem</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
   </si>
   <si>
     <t>TextFieldSearch</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx</t>
   </si>
   <si>
     <t>TextField</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
-  </si>
-  <si>
-    <t>ListItemSelect</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
   </si>
   <si>
     <t>HelpText</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
-  </si>
-  <si>
-    <t>ListItemColumn</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
-  </si>
-  <si>
-    <t>ListItemMultiSelect</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx</t>
-  </si>
-  <si>
-    <t>ListItem</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
   </si>
   <si>
     <t>Cell</t>
@@ -539,55 +539,55 @@
     <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/UI/NetworkSelectorList/NetworkSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/UnstakeTimeCard/UnstakeTimeCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/UnstakeTimeCard/UnstakeTimeCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
   </si>
   <si>
     <t>BottomSheet</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+  </si>
+  <si>
+    <t>Banner</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIBanner/SnapUIBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/CollectibleDetectionModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnMaintenanceBanner/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
   </si>
   <si>
     <t>Badge</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/AccountNetworkIndicator/AccountNetworkIndicator.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx</t>
   </si>
   <si>
     <t>Avatar</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/AccountNetworkIndicator/AccountNetworkIndicator.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx</t>
-  </si>
-  <si>
-    <t>Banner</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIBanner/SnapUIBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/CollectibleDetectionModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnMaintenanceBanner/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
   </si>
   <si>
     <t>Accordion</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx</t>
   </si>
   <si>
     <t>AccountListHeader</t>
@@ -608,58 +608,58 @@
     <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
   </si>
   <si>
+    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+  </si>
+  <si>
     <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Stake/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/ResourceToggle/ResourceToggle.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/ResourceToggle/ResourceToggle.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
-  </si>
-  <si>
     <t>BottomSheetDialog</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/index.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
+    <t>BannerAlert</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Wallet/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alert-banner/alert-banner.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx</t>
+  </si>
+  <si>
+    <t>BannerBase</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx</t>
   </si>
   <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx</t>
+  </si>
+  <si>
     <t>repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapUIAvatar/SnapUIAvatar.tsx, repos/metamask-mobile/app/components/UI/Identicon/index.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx</t>
   </si>
   <si>
-    <t>BannerBase</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx</t>
-  </si>
-  <si>
-    <t>BannerAlert</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Wallet/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alert-banner/alert-banner.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx</t>
-  </si>
-  <si>
     <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
   </si>
   <si>
     <t>BadgeCount</t>
@@ -689,10 +689,10 @@
     <t>Box</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/sections.config.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/Homepage/Homepage.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.stories.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsSettingsView.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Predict/hooks/usePredictToastRegistrations.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderRedirect.tsx, repos/metamask-mobile/app/components/UI/OnboardingAnimation/__mocks__/OnboardingAnimation.tsx, repos/metamask-mobile/app/components/UI/Notification/List/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/FoxAnimation/__mocks__/FoxAnimation.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionRow/SectionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionCard/SectionCard.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.stories.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perps/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/TokensSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/RewardsActivity.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportTeamGradient/PredictSportTeamGradient.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCardWrapper.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProgressBar/PerpsProgressBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Root/Root.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/ReferralStatsSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Cta.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AddRewardsAccount/AddRewardsAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/QuickAmounts/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TrendingView/sections.config.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/Homepage/Homepage.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.stories.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsSettingsView.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Predict/hooks/usePredictToastRegistrations.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderRedirect.tsx, repos/metamask-mobile/app/components/UI/OnboardingAnimation/__mocks__/OnboardingAnimation.tsx, repos/metamask-mobile/app/components/UI/Notification/List/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/FoxAnimation/__mocks__/FoxAnimation.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.stories.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionRow/SectionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionCard/SectionCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/TokensSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perps/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/RewardsActivity.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportTeamGradient/PredictSportTeamGradient.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCardWrapper.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictActionButtons.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProgressBar/PerpsProgressBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCarrousel.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Root/Root.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/ReferralStatsSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Cta.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AddRewardsAccount/AddRewardsAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/QuickAmounts/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHomeView/PerpsHomeView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageButtonGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx</t>
   </si>
   <si>
     <t>ButtonAnimated</t>
@@ -701,10 +701,10 @@
     <t>repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeviceAuthenticationButton/DeviceAuthenticationButton.tsx, repos/metamask-mobile/app/components/UI/AddressCopy/AddressCopy.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardButton/CardButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/SelectOptionSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/hooks/useRewardDashboardModals.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeviceAuthenticationButton/DeviceAuthenticationButton.tsx, repos/metamask-mobile/app/components/UI/AddressCopy/AddressCopy.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/UI/Card/routes/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardButton/CardButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/SelectOptionSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/hooks/useRewardDashboardModals.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx</t>
   </si>
   <si>
     <t>Jazzicon</t>
@@ -713,7 +713,7 @@
     <t>Maskicon</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/account-type-label/account-type-label.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/SwapEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/MusdDepositEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/CardEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/Perps/hooks/usePerpsToasts.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/PredictMarketDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportScoreboard/PredictSportScoreboard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicks.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSportCard/PredictMarketSportCard.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketRowItem/PredictMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomePositionList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedList.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedCarousel.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameDetailsFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsContent/PredictGameDetailsContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameChart/PredictGameChartContent.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivity/PredictActivity.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictBetButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHoursBanner/PerpsMarketHoursBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoadingSkeleton/PerpsLoadingSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDiscoveryBanner/PerpsDiscoveryBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTweetCard/MarketInsightsTweetCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendItem/MarketInsightsTrendItem.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsEntryCard/MarketInsightsEntryCard.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/DaimoPayModal/DaimoPayModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyingVeriffKYC.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SelectField.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/InputStepper/InputStepperDescriptionRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/account-type-label/account-type-label.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/ViewMoreCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictPositionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/MarketHoursContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/StakePreview/TronStakePreview.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/WaysToEarn.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/SwapEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/MusdDepositEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/CardEventDetails.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsTabBar/PredictMarketDetailsTabBar.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsPositions/PredictMarketDetailsPositions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx</t>
@@ -761,15 +761,15 @@
     <t>app/component-library/components-temp/ActionListItem/ActionListItem.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components/Toast/Toast.context.tsx</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Overlay/Overlay.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/base-components/TagBase/TagBase.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/Toast/Toast.context.tsx</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Overlay/Overlay.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components-temp/Tabs/TabsList/TabsList.tsx</t>
   </si>
   <si>
@@ -785,34 +785,46 @@
     <t>app/component-library/components-temp/MultichainAccounts/MultichainAddWalletActions/MultichainAddWalletActions.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components-temp/Buttons/ButtonToggle/ButtonToggle.tsx</t>
+  </si>
+  <si>
+    <t>app/component-library/components-temp/Buttons/ButtonSemantic/ButtonSemantic.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/components-temp/Buttons/ButtonPill/ButtonPill.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components-temp/Buttons/ButtonToggle/ButtonToggle.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components-temp/Buttons/ButtonHero/ButtonHero.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components-temp/Buttons/ButtonSemantic/ButtonSemantic.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components-temp/Accounts/AccountBalance/AccountBalance.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components/Texts/SensitiveText/SensitiveText.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/components/Tags/TagUrl/TagUrl.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/Texts/SensitiveText/SensitiveText.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components/Tags/Tag/Tag.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components/Select/SelectButton/SelectButton.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/components/Pickers/PickerNetwork/PickerNetwork.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/Select/SelectButton/SelectButton.tsx</t>
+    <t>app/component-library/components/List/ListItemSelect/ListItemSelect.tsx</t>
+  </si>
+  <si>
+    <t>app/component-library/components/List/ListItemMultiSelect/ListItemMultiSelect.tsx</t>
+  </si>
+  <si>
+    <t>app/component-library/components/List/ListItemColumn/ListItemColumn.tsx</t>
+  </si>
+  <si>
+    <t>app/component-library/components/List/ListItem/ListItem.tsx</t>
   </si>
   <si>
     <t>app/component-library/components/Form/TextFieldSearch/TextFieldSearch.tsx</t>
@@ -821,21 +833,9 @@
     <t>app/component-library/components/Form/TextField/TextField.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/List/ListItemSelect/ListItemSelect.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components/Form/HelpText/HelpText.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/List/ListItemColumn/ListItemColumn.tsx</t>
-  </si>
-  <si>
-    <t>app/component-library/components/List/ListItemMultiSelect/ListItemMultiSelect.tsx</t>
-  </si>
-  <si>
-    <t>app/component-library/components/List/ListItem/ListItem.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components/Cells/Cell/Cell.tsx</t>
   </si>
   <si>
@@ -845,15 +845,15 @@
     <t>app/component-library/components/BottomSheets/BottomSheet/BottomSheet.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components/Banners/Banner/Banner.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/components/Badges/Badge/Badge.tsx</t>
   </si>
   <si>
     <t>app/component-library/components/Avatars/Avatar/Avatar.tsx</t>
   </si>
   <si>
-    <t>app/component-library/components/Banners/Banner/Banner.tsx</t>
-  </si>
-  <si>
     <t>app/component-library/components/Accordions/Accordion/Accordion.tsx</t>
   </si>
   <si>
@@ -866,10 +866,10 @@
     <t>app/component-library/components/BottomSheets/BottomSheet/foundation/BottomSheetDialog/BottomSheetDialog.tsx</t>
   </si>
   <si>
+    <t>app/component-library/components/Banners/Banner/variants/BannerAlert/BannerAlert.tsx</t>
+  </si>
+  <si>
     <t>app/component-library/components/Banners/Banner/foundation/BannerBase/BannerBase.tsx</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Banners/Banner/variants/BannerAlert/BannerAlert.tsx</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1383,7 @@
         <v>1958</v>
       </c>
       <c r="E7">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F7" t="s">
         <v>19</v>
@@ -1440,53 +1440,53 @@
         <v>25</v>
       </c>
       <c r="D10">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11">
+        <v>80</v>
+      </c>
+      <c r="E11">
+        <v>51</v>
+      </c>
+      <c r="F11" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>365</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>365</v>
+      </c>
+      <c r="E12" t="s">
         <v>32</v>
       </c>
-      <c r="C12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1497,16 +1497,16 @@
         <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1517,36 +1517,36 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D14">
-        <v>369</v>
-      </c>
-      <c r="E14">
-        <v>65</v>
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15">
+        <v>369</v>
+      </c>
+      <c r="E15">
+        <v>65</v>
+      </c>
+      <c r="F15" t="s">
         <v>39</v>
-      </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D15">
-        <v>7</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1637,33 +1637,33 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" t="s">
         <v>53</v>
       </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
       <c r="D21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" t="s">
         <v>55</v>
@@ -1720,10 +1720,10 @@
         <v>60</v>
       </c>
       <c r="D24">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
         <v>62</v>
@@ -1740,27 +1740,27 @@
         <v>63</v>
       </c>
       <c r="D25">
+        <v>11</v>
+      </c>
+      <c r="E25">
         <v>1</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
       <c r="F25" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" t="s">
         <v>66</v>
       </c>
-      <c r="C26" t="s">
-        <v>65</v>
-      </c>
       <c r="D26">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1771,22 +1771,22 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B27" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" t="s">
         <v>68</v>
       </c>
-      <c r="C27" t="s">
-        <v>67</v>
-      </c>
       <c r="D27">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="E27">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1814,16 +1814,16 @@
         <v>72</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D29">
         <v>3168</v>
       </c>
       <c r="E29">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F29" t="s">
         <v>73</v>
@@ -1879,13 +1879,13 @@
         <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>25</v>
@@ -2100,21 +2100,21 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
         <v>113</v>
-      </c>
-      <c r="B15" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15">
-        <v>11</v>
-      </c>
-      <c r="D15" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>114</v>
       </c>
       <c r="B16" t="s">
         <v>87</v>
@@ -2128,41 +2128,41 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17">
+        <v>152</v>
+      </c>
+      <c r="D17" t="s">
         <v>116</v>
-      </c>
-      <c r="B17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
         <v>87</v>
       </c>
       <c r="C18">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="B19" t="s">
         <v>87</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>119</v>
@@ -2170,41 +2170,41 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
         <v>120</v>
-      </c>
-      <c r="B20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
         <v>87</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="B22" t="s">
         <v>87</v>
       </c>
       <c r="C22">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D22" t="s">
         <v>123</v>
@@ -2288,7 +2288,7 @@
         <v>87</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" t="s">
         <v>135</v>
@@ -2302,7 +2302,7 @@
         <v>87</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -2316,7 +2316,7 @@
         <v>87</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D30" t="s">
         <v>139</v>
@@ -2330,7 +2330,7 @@
         <v>87</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D31" t="s">
         <v>141</v>
@@ -2372,7 +2372,7 @@
         <v>87</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
         <v>146</v>
@@ -2386,7 +2386,7 @@
         <v>87</v>
       </c>
       <c r="C35">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -2428,7 +2428,7 @@
         <v>87</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>153</v>
@@ -2442,7 +2442,7 @@
         <v>87</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D39" t="s">
         <v>155</v>
@@ -2450,77 +2450,77 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>156</v>
       </c>
       <c r="B40" t="s">
         <v>87</v>
       </c>
       <c r="C40">
-        <v>305</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" t="s">
         <v>87</v>
       </c>
       <c r="C41">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" t="s">
         <v>87</v>
       </c>
       <c r="C42">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="B43" t="s">
         <v>87</v>
       </c>
       <c r="C43">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
         <v>87</v>
       </c>
       <c r="C44">
-        <v>30</v>
+        <v>305</v>
       </c>
       <c r="D44" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B45" t="s">
         <v>87</v>
@@ -2529,32 +2529,32 @@
         <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" t="s">
         <v>87</v>
       </c>
       <c r="C46">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
         <v>87</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D47" t="s">
         <v>169</v>
@@ -2568,7 +2568,7 @@
         <v>87</v>
       </c>
       <c r="C48">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
         <v>171</v>
@@ -2596,7 +2596,7 @@
         <v>87</v>
       </c>
       <c r="C50">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="D50" t="s">
         <v>174</v>
@@ -2604,13 +2604,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
         <v>87</v>
       </c>
       <c r="C51">
-        <v>365</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
         <v>175</v>
@@ -2618,13 +2618,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
         <v>87</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>365</v>
       </c>
       <c r="D52" t="s">
         <v>176</v>
@@ -2632,13 +2632,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
         <v>87</v>
       </c>
       <c r="C53">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
         <v>177</v>
@@ -2646,13 +2646,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="B54" t="s">
         <v>87</v>
       </c>
       <c r="C54">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="D54" t="s">
         <v>178</v>
@@ -2674,27 +2674,27 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
         <v>87</v>
       </c>
       <c r="C56">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>42</v>
       </c>
       <c r="B57" t="s">
         <v>87</v>
       </c>
       <c r="C57">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D57" t="s">
         <v>183</v>
@@ -2708,7 +2708,7 @@
         <v>87</v>
       </c>
       <c r="C58">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D58" t="s">
         <v>185</v>
@@ -2736,7 +2736,7 @@
         <v>87</v>
       </c>
       <c r="C60">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D60" t="s">
         <v>188</v>
@@ -2800,7 +2800,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
         <v>87</v>
@@ -2814,13 +2814,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
         <v>87</v>
       </c>
       <c r="C66">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D66" t="s">
         <v>197</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
         <v>87</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
         <v>198</v>
@@ -2842,13 +2842,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B68" t="s">
         <v>87</v>
       </c>
       <c r="C68">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
         <v>199</v>
@@ -2870,125 +2870,125 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="B70" t="s">
         <v>87</v>
       </c>
       <c r="C70">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>204</v>
       </c>
       <c r="B71" t="s">
         <v>87</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B72" t="s">
         <v>87</v>
       </c>
       <c r="C72">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D72" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B73" t="s">
         <v>87</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D73" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
         <v>87</v>
       </c>
       <c r="C74">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D74" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
         <v>87</v>
       </c>
       <c r="C75">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D75" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B76" t="s">
         <v>87</v>
       </c>
       <c r="C76">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
         <v>87</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D77" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
         <v>87</v>
       </c>
       <c r="C78">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D78" t="s">
         <v>212</v>
@@ -3024,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -3035,18 +3035,18 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -3057,23 +3057,23 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -3123,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,7 +3167,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -3194,7 +3194,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>65</v>
@@ -3211,12 +3211,12 @@
         <v>0</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B20">
         <v>3</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>51</v>
@@ -3238,13 +3238,13 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3266,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="C26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3310,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="C29" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,7 +3332,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="C31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3351,7 +3351,7 @@
         <v>17</v>
       </c>
       <c r="B32">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C32" t="s">
         <v>232</v>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3395,10 +3395,10 @@
         <v>72</v>
       </c>
       <c r="B36">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="C36" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -3610,44 +3610,44 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" t="s">
         <v>248</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
         <v>249</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B17" t="s">
         <v>250</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -3728,7 +3728,7 @@
         <v>256</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
         <v>135</v>
@@ -3742,7 +3742,7 @@
         <v>257</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D24" t="s">
         <v>137</v>
@@ -3756,7 +3756,7 @@
         <v>258</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -3770,7 +3770,7 @@
         <v>259</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="s">
         <v>141</v>
@@ -3798,7 +3798,7 @@
         <v>261</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
         <v>146</v>
@@ -3812,7 +3812,7 @@
         <v>262</v>
       </c>
       <c r="C29">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="D29" t="s">
         <v>148</v>
@@ -3840,7 +3840,7 @@
         <v>264</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D31" t="s">
         <v>153</v>
@@ -3854,7 +3854,7 @@
         <v>265</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D32" t="s">
         <v>155</v>
@@ -3862,86 +3862,86 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
         <v>266</v>
       </c>
       <c r="C33">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B34" t="s">
         <v>267</v>
       </c>
       <c r="C34">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
         <v>268</v>
       </c>
       <c r="C35">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B36" t="s">
         <v>269</v>
       </c>
       <c r="C36">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B37" t="s">
         <v>270</v>
       </c>
       <c r="C37">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B38" t="s">
         <v>271</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D38" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -3952,7 +3952,7 @@
         <v>272</v>
       </c>
       <c r="C39">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
         <v>171</v>
@@ -3983,7 +3983,7 @@
         <v>91</v>
       </c>
       <c r="D41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -4002,16 +4002,16 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B43" t="s">
         <v>276</v>
       </c>
       <c r="C43">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -4022,7 +4022,7 @@
         <v>277</v>
       </c>
       <c r="C44">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D44" t="s">
         <v>185</v>
@@ -4036,7 +4036,7 @@
         <v>278</v>
       </c>
       <c r="C45">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D45" t="s">
         <v>188</v>
@@ -4100,30 +4100,30 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
         <v>283</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D50" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B51" t="s">
         <v>284</v>
       </c>
       <c r="C51">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -4131,13 +4131,13 @@
         <v>72</v>
       </c>
       <c r="B52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C52">
         <v>970</v>
       </c>
       <c r="D52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/metrics/mobile-component-metrics-2026-02-24.xlsx
+++ b/metrics/mobile-component-metrics-2026-02-24.xlsx
@@ -74,7 +74,7 @@
     <t>app/component-library/components/Texts/Text/Text.tsx</t>
   </si>
   <si>
-    <t>22.97%</t>
+    <t>22.94%</t>
   </si>
   <si>
     <t>Icon</t>
@@ -92,6 +92,12 @@
     <t>app/component-library/components/Form/Label/Label.tsx</t>
   </si>
   <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Cards/Card/Card.tsx</t>
+  </si>
+  <si>
     <t>ButtonIcon</t>
   </si>
   <si>
@@ -131,12 +137,6 @@
     <t>14.98%</t>
   </si>
   <si>
-    <t>Card</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Cards/Card/Card.tsx</t>
-  </si>
-  <si>
     <t>BottomSheetFooter</t>
   </si>
   <si>
@@ -164,6 +164,18 @@
     <t>app/component-library/components/Form/TextField/foundation/Input/Input.tsx</t>
   </si>
   <si>
+    <t>ButtonLink</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Buttons/Button/variants/ButtonLink/ButtonLink.tsx</t>
+  </si>
+  <si>
+    <t>TextButton</t>
+  </si>
+  <si>
+    <t>7.14%</t>
+  </si>
+  <si>
     <t>ButtonBase</t>
   </si>
   <si>
@@ -173,70 +185,58 @@
     <t>20.00%</t>
   </si>
   <si>
-    <t>ButtonLink</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Buttons/Button/variants/ButtonLink/ButtonLink.tsx</t>
-  </si>
-  <si>
-    <t>TextButton</t>
-  </si>
-  <si>
-    <t>7.14%</t>
-  </si>
-  <si>
     <t>BadgeNetwork</t>
   </si>
   <si>
     <t>app/component-library/components/Badges/Badge/variants/BadgeNetwork/BadgeNetwork.tsx</t>
   </si>
   <si>
+    <t>AvatarToken</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarToken/AvatarToken.tsx</t>
+  </si>
+  <si>
+    <t>17.50%</t>
+  </si>
+  <si>
+    <t>AvatarNetwork</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarNetwork/AvatarNetwork.tsx</t>
+  </si>
+  <si>
+    <t>8.33%</t>
+  </si>
+  <si>
+    <t>AvatarIcon</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarIcon/AvatarIcon.tsx</t>
+  </si>
+  <si>
+    <t>AvatarFavicon</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarFavicon/AvatarFavicon.tsx</t>
+  </si>
+  <si>
+    <t>AvatarAccount</t>
+  </si>
+  <si>
+    <t>app/component-library/components/Avatars/Avatar/variants/AvatarAccount/AvatarAccount.tsx</t>
+  </si>
+  <si>
     <t>AvatarBase</t>
   </si>
   <si>
     <t>app/component-library/components/Avatars/Avatar/foundation/AvatarBase/AvatarBase.tsx</t>
   </si>
   <si>
-    <t>AvatarNetwork</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarNetwork/AvatarNetwork.tsx</t>
-  </si>
-  <si>
-    <t>8.33%</t>
-  </si>
-  <si>
-    <t>AvatarIcon</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarIcon/AvatarIcon.tsx</t>
-  </si>
-  <si>
-    <t>AvatarFavicon</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarFavicon/AvatarFavicon.tsx</t>
-  </si>
-  <si>
-    <t>AvatarToken</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarToken/AvatarToken.tsx</t>
-  </si>
-  <si>
-    <t>17.50%</t>
-  </si>
-  <si>
-    <t>AvatarAccount</t>
-  </si>
-  <si>
-    <t>app/component-library/components/Avatars/Avatar/variants/AvatarAccount/AvatarAccount.tsx</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>20.58%</t>
+    <t>20.56%</t>
   </si>
   <si>
     <t>Old Component</t>
@@ -275,25 +275,52 @@
     <t>File Paths</t>
   </si>
   <si>
+    <t>app/component-library/components/Toast/ToastModal.testIds.ts</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Nav/App/App.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx</t>
+  </si>
+  <si>
+    <t>ToastContextWrapper</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Root/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
+  </si>
+  <si>
+    <t>Overlay</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx</t>
+  </si>
+  <si>
+    <t>TagColored</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx</t>
+  </si>
+  <si>
     <t>TabEmptyState</t>
   </si>
   <si>
-    <t>app/component-library/components-temp/TitleSubpage/TitleSubpage.tsx</t>
-  </si>
-  <si>
     <t>repos/metamask-mobile/app/components/Views/UnifiedTransactionsView/UnifiedTransactionsView.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Transactions/index.js, repos/metamask-mobile/app/components/UI/TokensEmptyState/TokensEmptyState.tsx, repos/metamask-mobile/app/components/UI/DefiEmptyState/DefiEmptyState.tsx, repos/metamask-mobile/app/components/UI/CollectiblesEmptyState/CollectiblesEmptyState.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsEmptyState/PerpsEmptyState.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrdersList/OrdersList.tsx</t>
   </si>
   <si>
-    <t>TagColored</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx</t>
-  </si>
-  <si>
     <t>TabBar</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Nav/Main/MainNavigator.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Nav/Main/MainNavigator.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx</t>
   </si>
   <si>
     <t>SheetActions</t>
@@ -329,13 +356,13 @@
     <t>HeaderStackedStandard</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx</t>
   </si>
   <si>
     <t>HeaderCompactStandard</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/AddAsset.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectComponent/index.js, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AppInformation/index.js, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictFeed/PredictFeed.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/estimates-modal/estimates-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-modal/gas-fee-token-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/expandable/expandable.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
   </si>
   <si>
     <t>ConditionalScrollView</t>
@@ -362,31 +389,145 @@
     <t>repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Earn/components/OutputAmountTag/OutputAmountTag.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Nav/App/App.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx</t>
-  </si>
-  <si>
-    <t>ToastContextWrapper</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Root/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SkeletonItem.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenSkeleton/TrendingTokensSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteSkeleton/SiteSkeleton.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictSportCardFooter/PredictSportCardFooter.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPicksForCardItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPicks/PredictPickItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSkeleton/PredictMarketSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictHome/PredictHomeFeaturedSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsButtonsSkeleton/PredictDetailsButtonsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsContentSkeleton/PredictDetailsContentSkeleton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/TradingViewChart/TradingViewChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionsSkeleton/PerpsTransactionsSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRowSkeleton/PerpsRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountNetworkList/SmartAccountNetworkList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/UpcomingRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/SnapshotsTab/SnapshotsTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityTab.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/ActiveBoosts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/hero-row/hero-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/SnapshotsSection/SnapshotsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/components/PerpsMarketRowSkeleton/PerpsMarketRowSkeleton.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Views/PickComponent/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
-  </si>
-  <si>
-    <t>Overlay</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TradeWalletActions/TradeWalletActions.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx</t>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+  </si>
+  <si>
+    <t>SensitiveText</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx</t>
+  </si>
+  <si>
+    <t>TagUrl</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/UI/ApprovalTagUrl/ApprovalTagUrl.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingleSelector/AccountConnectSingleSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealPrivateKey/RevealPrivateKey.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
+  </si>
+  <si>
+    <t>SelectButton</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx</t>
+  </si>
+  <si>
+    <t>PickerNetwork</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/PaymentRequest/index.js, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx</t>
+  </si>
+  <si>
+    <t>ListItemSelect</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
+  </si>
+  <si>
+    <t>ListItemMultiSelect</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx</t>
+  </si>
+  <si>
+    <t>ListItemColumn</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx</t>
+  </si>
+  <si>
+    <t>ListItem</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
+  </si>
+  <si>
+    <t>TextFieldSearch</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
+  </si>
+  <si>
+    <t>TextField</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
+  </si>
+  <si>
+    <t>HelpText</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/UI/NetworkSelectorList/NetworkSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/UnstakeTimeCard/UnstakeTimeCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
+  </si>
+  <si>
+    <t>BottomSheet</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx</t>
+  </si>
+  <si>
+    <t>Banner</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIBanner/SnapUIBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/CollectibleDetectionModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnMaintenanceBanner/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+  </si>
+  <si>
+    <t>Badge</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/AccountNetworkIndicator/AccountNetworkIndicator.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx</t>
+  </si>
+  <si>
+    <t>Avatar</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
+  </si>
+  <si>
+    <t>Accordion</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx</t>
   </si>
   <si>
     <t>TabsList</t>
@@ -407,28 +548,34 @@
     <t>repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx</t>
   </si>
   <si>
+    <t>MultichainAddWalletActions</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx</t>
+  </si>
+  <si>
     <t>MultichainAddressRow</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx</t>
   </si>
   <si>
-    <t>MultichainAddWalletActions</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx</t>
+    <t>ButtonToggle</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
+  </si>
+  <si>
+    <t>ButtonSemantic</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx</t>
   </si>
   <si>
     <t>ButtonPill</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
-  </si>
-  <si>
-    <t>ButtonToggle</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
+    <t>repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx</t>
   </si>
   <si>
     <t>ButtonHero</t>
@@ -437,159 +584,12 @@
     <t>repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActionButtons/PredictClaimButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
   </si>
   <si>
-    <t>ButtonSemantic</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx</t>
-  </si>
-  <si>
     <t>AccountBalance</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/ApproveTransactionHeader/ApproveTransactionHeader.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/RestoreWallet.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletRestored.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/QRScanner/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsBox.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetailsInformationRow.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/Asset/ActivityHeader.tsx, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/Asset/index.js, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AssetDetails/index.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Clipboard.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/AesCryptoTestForm.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AddAccountActions/AddAccountActions.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInfoRow/SnapUIInfoRow.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICard/SnapUICard.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddress/SnapUIAddress.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/TemplateRenderer/TemplateRenderer.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/SrpWordSuggestions/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SrpInputGrid/index.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SecurityOptionToggle/SecurityOptionToggle.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/NavbarTitle/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/ConnectHeader/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionality.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AddressInputs/index.js, repos/metamask-mobile/app/components/UI/AccountFromToInfoCard/AddressFrom.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountOverview/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountInfoCard/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/index.js, repos/metamask-mobile/app/components/Base/TokenIcon/index.tsx, repos/metamask-mobile/app/components/Base/Title/Title.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/sectionHeader.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/PushNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/MainNotificationToggle.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworkDetailsCheckSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/IPFSGatewaySettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DisplayNFTMediaSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/BatchAccountBalanceSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectTokensSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/AutoDetectNFTSettings/index.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSuccess/DefaultSettings/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/ConnectHardware/SelectHardware/index.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/Transactions/RetryModal/index.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/TokenDetailsInlineHeader.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/AssetOverviewContent.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/FiatDisplay/FiatDisplay.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/BalanceChangeRow/BalanceChangeRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Perps/Debug/HIP3DebugView.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Content.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/LedgerModals/Steps/SearchingForDeviceStep.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncToggle/BackupAndSyncToggle.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useMusdConversionNavbar.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsListItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Price/Price.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/ChartNavigationButton/ChartNavigationButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/useAccountTypeUpgrade.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/title/title.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/smart-contract-with-logo/smart-contract-with-logo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/qr-info/qr-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/pay-token-amount/pay-token-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nested-transaction-data/nested-transaction-data.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/hero-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/data-tree/data-field.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBannerLink.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissions/SnapPermissions.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/BlockaidSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/RpcUrlInput.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/ResetAccountModal/ResetAccountModal.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Title/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/StakingProviderField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenLogo/TrendingTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakeButton/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsReferralCodeTag/RewardsReferralCodeTag.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAmountDisplay/PredictAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/PredictDetailsChart.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWatchlistMarkets/PerpsWatchlistMarkets.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionItem/PerpsTransactionItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTokenLogo/PerpsTokenLogo.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTransactionDetailAssetHero/PerpsTransactionDetailAssetHero.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTabControlBar/PerpsTabControlBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsSlider/PerpsSlider.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookTable/PerpsOrderBookTable.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderBookDepthChart/PerpsOrderBookDepthChart.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOHLCVBar/PerpsOHLCVBar.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTradesList/PerpsMarketTradesList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketRowItem/PerpsMarketRowItem.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketList/PerpsMarketList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLoader/PerpsLoader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketBalanceActions/PerpsMarketBalanceActions.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverage/PerpsLeverage.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFillTag/PerpsFillTag.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFeesDisplay/PerpsFeesDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsEmptyBalance/PerpsEmptyBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsTestnetToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsProviderToggle.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCompactOrderRow/PerpsCompactOrderRow.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCard/PerpsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlestickChartIntervalSelector/PerpsCandlestickChartIntervalSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBadge/PerpsBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAmountDisplay/PerpsAmountDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceDisplay.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/LivePriceDisplay/LivePriceHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/FundingCountdown/FundingCountdown.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitProgressBar/SpendingLimitProgressBar.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeStepDescription.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BridgeActivityItemTxSegments.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteCountdownTimer/QuoteCountdownTimer.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/MarketDetailsList/MarketDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TokenDetails/TokenDetailsList/TokenDetailsList.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/EditGasFeeLegacyUpdate/index.jsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressList/AddressList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/transactions/custom-amount/custom-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/total-row/total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/receive-row/receive-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-time-row/bridge-time-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/percentage-row/percentage-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-withdraw-balance/predict-withdraw-balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-amount/predict-claim-amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/bridge-fee-row/bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/personal-sign/message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/priority-fee-input/priority-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-speed/gas-speed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-price-input/gas-price-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/max-base-fee-input/max-base-fee-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-option/gas-option.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alerts/alert-message/alert-message.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-total-row/transaction-details-total-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-row/transaction-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-paid-with-row/transaction-details-paid-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-bridge-fee-row/transaction-details-bridge-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-network-fee-row/transaction-details-network-fee-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-date-row/transaction-details-date-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-account-row/transaction-details-account-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-hero/transaction-details-hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/pill/pill.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/hero/hero.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/AutoLock/AutoLock.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerHeader/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingCta/StakingCta.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositPhoneField/DepositPhoneField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/ChartLegend.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/WithdrawalFeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/TPSLCountWarningTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/content/FeesTooltipContent.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsChart/components/TimeframeSelector.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-details/staking-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-and-origin-row/network-and-origin-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/from-to-row/from-to-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/advanced-details-row/advanced-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/LegalLinks/LegalLinks.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/ChartTimespanButtonGroup/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/InteractiveTimespanChart/GraphTooltip/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsTimePeriod/EarningsTimePeriod.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryChart/EarningsHistoryChart.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositInfoSection/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/typed-sign-decoded/typed-sign-decoded.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/info-date/info-date.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
-  </si>
-  <si>
-    <t>TagUrl</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/UI/ApprovalTagUrl/ApprovalTagUrl.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
-  </si>
-  <si>
-    <t>SensitiveText</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionGroupTokens.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiProtocolPositionDetails.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/UI/AssetElement/index.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPosition/PredictPosition.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionResolved/PredictPositionResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictActivityDetail/PredictActivityDetail.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/BalanceChange/AccountGroupBalanceChange.tsx, repos/metamask-mobile/app/components/UI/Assets/components/Balance/AccountGroupBalance.tsx</t>
-  </si>
-  <si>
-    <t>Tag</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingleSelector/AccountConnectSingleSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealPrivateKey/RevealPrivateKey.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx</t>
-  </si>
-  <si>
-    <t>PickerNetwork</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/PaymentRequest/index.js, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/ManageNetworks/ManageNetworks.tsx</t>
-  </si>
-  <si>
-    <t>SelectButton</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Base/SelectorButton.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletRecovery/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/RestoreWallet/WalletResetNeeded.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftOptions/NftOptions.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/NftDetails/NftDetails.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep2/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AccountAction/AccountAction.tsx, repos/metamask-mobile/app/components/Snaps/SnapUILink/SnapUILink.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIIcon/SnapUIIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICopyable/SnapUICopyable.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/SimulationDetails.tsx, repos/metamask-mobile/app/components/UI/SDKFeedback/index.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/QRHardware/AnimatedQRScanner.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/MaliciousDappIndicators.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/ButtonReveal/index.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/UI/BackupAlert/BackupAlert.tsx, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/TrendingTokens/TrendingTokensFullView/TrendingTokensFullView.tsx, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AddAccount/AddAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/StockBadge/StockBadge.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Stake/components/EstimatedAnnualRewardsCard.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Empty/index.tsx, repos/metamask-mobile/app/components/UI/Identity/BackupAndSyncFeaturesToggles/BackupAndSyncFeaturesToggles.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/hooks/useEarnToasts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/PriceChart/PriceChart.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/MarketClosedActionButton/MarketClosedActionButton.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/signature-message-section/signature-message-section.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-spending-cap-button/edit-spending-cap-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/batched-transactions-tag/batched-transactions-tag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapVersionTag/SnapVersionTag.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDescription/SnapDescription.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/CustomNotificationsRow/index.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/PermissionsSettings/PermissionItem/PermissionItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/Wallet.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/SecretRecoveryPhrase.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/components/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardPointsAnimation/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/PaymentMethodPill/PaymentMethodPill.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictShareButton/PredictShareButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionsHeader/PredictPositionsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictNewButton/PredictNewButton.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcomeResolved/PredictMarketOutcomeResolved.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictDetailsHeaderSkeleton/PredictDetailsHeaderSkeleton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsWebSocketHealthToast/PerpsWebSocketHealthToast.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTimeDurationSelector/PerpsTimeDurationSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsRecentActivityList/PerpsRecentActivityList.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPriceDeviationWarning/PerpsPriceDeviationWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOICapWarning/PerpsOICapWarning.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTypeSection/PerpsMarketTypeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketStatisticsCard/PerpsMarketStatisticsCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketTabs/PerpsMarketTabs.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortDropdowns/PerpsMarketSortDropdowns.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketCategoryBadge/PerpsMarketCategoryBadge.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeSection/PerpsHomeSection.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsHomeHeader/PerpsHomeHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCloseSummary/PerpsCloseSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodSelector/PerpsCandlePeriodSelector.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTabView/PerpsTabView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketListView/PerpsMarketListView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Card/components/SpendingLimitWarning/SpendingLimitWarning.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/StepProgressBarItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/PulsingCircle.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsRecipientKeyValueRow/QuoteDetailsRecipientKeyValueRow.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteDetailsCard/QuoteDetailsCard.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/FlipQuoteButton/index.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/pay-with-row/pay-with-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/selected-gas-fee-token/selected-gas-fee-token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-list-item/gas-fee-token-list-item.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-status/transaction-details-status.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-section-accordion/info-section-accordion.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/inline-alert/inline-alert.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-row.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/components/AddAccountItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccount/SmartAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/ExportCredentials/ExportCredentials.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/UpsellBanner/UpsellBannerBody/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/QuoteDisplay.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositDateField/DepositDateField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/BankDetailRow/BankDetailRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetOverviewCta/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/gas-fee-details-row/gas-fee-details-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/copy-icon/copy-icon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsStatus/PredictMarketDetailsStatus.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsHeader/PredictMarketDetailsHeader.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsOutcomes/PredictMarketDetailsOutcomes.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsAbout/PredictMarketDetailsAbout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/display-url/display-url.tsx</t>
-  </si>
-  <si>
-    <t>TextFieldSearch</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/BridgeTokenSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/asset/asset.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
-  </si>
-  <si>
-    <t>TextField</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-field-with-label/text-field-with-label.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/LimitOptionItem.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Box.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/StateSelector/StateSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositTextField/DepositTextField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistory/EarningsHistoryList/EarningsHistoryList.tsx</t>
-  </si>
-  <si>
-    <t>ListItemSelect</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
-  </si>
-  <si>
-    <t>HelpText</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIRadioGroup/SnapUIRadioGroup.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIInput/SnapUIInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUICheckbox/SnapUICheckbox.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx</t>
-  </si>
-  <si>
-    <t>ListItemColumn</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/MenuItem/MenuItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ListItemColumnEnd.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/ProviderSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentMethodListSkeleton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx</t>
-  </si>
-  <si>
-    <t>ListItemMultiSelect</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx</t>
-  </si>
-  <si>
-    <t>ListItem</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/SettingsDrawer/index.js, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AmountInput.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNavigationCard/PerpsNavigationCard.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Card/components/ManageCardListItem/ManageCardListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/PrivacySection/PrivacySection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonPaymentMethod/SkeletonPaymentMethod.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/SkeletonQuote/SkeletonQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx</t>
-  </si>
-  <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/UI/NetworkSelectorList/NetworkSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/EvmAccountSelectorList/EvmAccountSelectorList.tsx, repos/metamask-mobile/app/components/UI/CustomNetworkSelector/CustomNetworkSelector.tsx, repos/metamask-mobile/app/components/UI/CaipAccountSelectorList/CaipAccountSelectorList.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapElement/SnapElement.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/SnapDetails/SnapDetails.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/hooks/useOnboardingHeader.tsx, repos/metamask-mobile/app/components/Views/TokensFullView/TokensFullView.tsx, repos/metamask-mobile/app/components/Views/QRTabSwitcher/QRTabSwitcher.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIAddressInput/SnapUIAddressInput.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/Tabs/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/HintModal/index.js, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/BrowserUrlBar/BrowserUrlBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/Identity/BackupAndSyncSettings.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenListControlBar/TokenListControlBar.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/flat-nav-header/flat-nav-header.tsx, repos/metamask-mobile/app/components/Views/Snaps/components/KeyringAccountListItem/KeyringAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingEarnings/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeSummary/PredictFeeSummary.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderHeader/PerpsOrderHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketHeader/PerpsMarketHeader.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsChartFullscreenModal/PerpsChartFullscreenModal.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsPositionsView/PerpsPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/InputDisplay/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/ApprovalText/ApprovalTooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/multiple-alert-modal/multiple-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/predict-claim-info/predict-claim-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-modal-header/gas-modal-header.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-summary/transaction-details-summary.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/text-with-tooltip/text-with-tooltip.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/navbar/navbar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/copy-button/copy-button.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/Tooltip/Tooltip.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/ScamWarningIcon/ScamWarningIcon.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Settings/RegionSelector/RegionSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/native-value-display/native-value-display.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/simulation/components/value-display/value-display.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/WalletCreationError/SocialLoginErrorSheet.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/WalletCreationError/SRPErrorScreen.tsx, repos/metamask-mobile/app/components/Views/SocialLoginIosUser/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/RevealPrivateCredential/RevealPrivateCredential.tsx, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/ResetPassword/index.js, repos/metamask-mobile/app/components/Views/OnboardingSuccess/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/OAuthRehydration/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/Onboarding/index.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainTransactionsView/MultichainTransactionsFooter.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/Login/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ManualBackupStep1/index.tsx, repos/metamask-mobile/app/components/Views/ImportNewSecretRecoveryPhrase/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportPrivateKey/index.tsx, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ImportFromSecretRecoveryPhrase/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChoosePassword/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AesCryptoTestForm/Form.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccount.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountStatus/index.tsx, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Views/AccountBackupStep1/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIFooterButton/SnapUIFooterButton.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/UpdateNeeded/UpdateNeeded.tsx, repos/metamask-mobile/app/components/UI/Transactions/TransactionsFooter.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SheetActionView/SheetActionVIew.tsx, repos/metamask-mobile/app/components/UI/SettingsButtonSection/index.tsx, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PhishingModal/index.js, repos/metamask-mobile/app/components/UI/OptinMetrics/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/UI/CollectibleMedia/CollectibleMedia.tsx, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/UI/ActionView/index.js, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/transactions/SmartTransactionStatus/SmartTransactionStatus.tsx, repos/metamask-mobile/app/components/Views/Snaps/SnapSettings/SnapSettings.tsx, repos/metamask-mobile/app/components/Views/Settings/NotificationsSettings/ResetNotificationsButton.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/SecuritySettings.tsx, repos/metamask-mobile/app/components/Views/Settings/DeveloperOptions/SentryTest.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/Settings/ExperimentalSettings/index.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionsManager.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/index.js, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/QuizContent/QuizContent.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/Notifications/OptIn/index.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkConnect/NetworkConnectMultiSelector/NetworkConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/MultichainAccountsIntroModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/Identity/TurnOnBackupAndSync/TurnOnBackupAndSync.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectSingle/AccountConnectSingle.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/Notification/SwitchLoadingModal/Loader.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Notification/Modal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MusdDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/edit-amount-keyboard/edit-amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/deposit-keyboard/deposit-keyboard.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeleteMetaMetricsData.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearCookiesSection.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/BlockExplorerFooter.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Footers/AnnouncementCtaFooter.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/ScamWarningModal/ScamWarningModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictBuyPreview/PredictBuyPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictPositionDetail/PredictPositionDetail.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOffline/PredictOffline.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketSingle/PredictMarketSingle.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketMultiple/PredictMarketMultiple.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictMarketOutcome/PredictMarketOutcome.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictKeypad/PredictKeypad.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsTutorialCarousel/PerpsTutorialCarousel.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsStopLossPromptBanner/PerpsStopLossPromptBanner.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsPositionCard/PerpsPositionCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOpenOrderCard/PerpsOpenOrderCard.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsErrorState/PerpsErrorState.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsHIP3DebugButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsDeveloperOptionsSection/PerpsConnectionErrorButton.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsConnectionErrorView/PerpsConnectionErrorView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsPositionTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsOrderTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTransactionsView/PerpsFundingTransactionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTPSLView/PerpsTPSLView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsOrderView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderDetailsView/PerpsOrderDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsMarketDetailsView/PerpsMarketDetailsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsHeroCardView/PerpsHeroCardView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsClosePositionView/PerpsClosePositionView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsAdjustMarginView/PerpsAdjustMarginView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EmptyStateCta/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/EarnWithdrawInputView.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnMusdConversionEducationView/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnInputView/EarnInputView.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SignUp.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/SetPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PersonalDetails.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCPending.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/PhysicalAddress.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/KYCFailed.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmEmail.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardMessageBox/CardMessageBox.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmPhoneNumber.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardDeveloperOptionsSection/CardDeveloperOptionsSection.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/Complete.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ChooseYourCard/ChooseYourCard.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/SpendingLimit.tsx, repos/metamask-mobile/app/components/UI/Card/Views/ReviewOrder/ReviewOrder.tsx, repos/metamask-mobile/app/components/UI/Card/Views/OrderCompleted/OrderCompleted.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardHome/CardHome.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardAuthentication/CardAuthentication.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionDetails.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenInputArea/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsConfirmButton/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/QuickPickButtons.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/edit-spending-cap-modal/edit-spending-cap-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-gas-price-modal/advanced-gas-price-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/alert-modal/alert-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/advanced-eip1559-modal/advanced-eip1559-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/custom-amount-info/custom-amount-info.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/developer/confirmations-developer-options/confirmations-developer-options.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/activity/transaction-details-retry/transaction-details-retry.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ClearPrivacy/ClearPrivacy.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ChangePassword/ChangePassword.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/MetaMetricsAndDataCollectionSection/MetaMetricsAndDataCollectionSection.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/RemoveAccount/RemoveAccount.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/components/PredictMarketCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingButtons/StakingButtons.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/ErrorView/ErrorView.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/VerifyIdentity/VerifyIdentity.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OrderProcessing/OrderProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/OtpCode/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterEmail/EnterEmail.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/KycProcessing/KycProcessing.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BankDetails/BankDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/AdditionalVerification/AdditionalVerification.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/Quote/Quote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/CustomAction/CustomAction.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeys.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/Settings.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Settings/ActivationKeyForm.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/OrderDetails/OrderDetails.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingButtons/TronStakingButtons.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Earnings/EarningsHistoryButton/EarningsHistoryButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/amount/amount-keyboard/amount-keyboard.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ConfirmationFooter/FooterButtonGroup/FooterButtonGroup.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictMarketDetails/components/PredictMarketDetailsActions/PredictMarketDetailsActions.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Snaps/components/SnapPermissionCell/SnapPermissionCell.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/Sections/SectionTypes/SectionCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/UnstakeTimeCard/UnstakeTimeCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/RewardsCard/RewardsCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/Snaps/SnapDialogApproval/SnapDialogApproval.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/Approvals/SnapAccountCustomNameApproval/SnapAccountCustomNameApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/Views/TokenDetails.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/footer/footer.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Stake/components/LearnMoreModal/LearnMoreModalFooter.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapSuccess/InstallSnapSuccess.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapError/InstallSnapError.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapPermissionsRequest/InstallSnapPermissionsRequest.tsx, repos/metamask-mobile/app/components/Approvals/InstallSnapApproval/components/InstallSnapConnectionRequest/InstallSnapConnectionRequest.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/Approval/TemplateConfirmation/TemplateConfirmation.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ConfirmationFooter/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUITooltip/SnapUITooltip.tsx, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/NetworkModal/NetworkAdded/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictSellPreview/PredictSellPreview.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx</t>
-  </si>
-  <si>
-    <t>BottomSheet</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/WalletActions/WalletActions.tsx, repos/metamask-mobile/app/components/Views/TooltipModal/index.tsx, repos/metamask-mobile/app/components/Views/SuccessErrorSheet/index.tsx, repos/metamask-mobile/app/components/Views/ShowTokenIdSheet/ShowTokenIdSheet.tsx, repos/metamask-mobile/app/components/Views/ShowIpfsGatewaySheet/ShowIpfsGatewaySheet.tsx, repos/metamask-mobile/app/components/Views/ShowDisplayMediaNFTSheet/ShowDisplayNFTMediaSheet.tsx, repos/metamask-mobile/app/components/Views/SelectSRP/SelectSRPBottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/OnboardingSheet/index.tsx, repos/metamask-mobile/app/components/Views/OriginSpamModal/OriginSpamModal.tsx, repos/metamask-mobile/app/components/Views/NFTAutoDetectionModal/NFTAutoDetectionModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/MultiRpcModal/MultiRpcModal.tsx, repos/metamask-mobile/app/components/Views/ExperienceEnhancerModal/index.tsx, repos/metamask-mobile/app/components/Views/DataCollectionModal/index.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/index.tsx, repos/metamask-mobile/app/components/Views/ChangeInSimulationModal/ChangeInSimulationModal.tsx, repos/metamask-mobile/app/components/Views/AssetOptions/AssetOptions.tsx, repos/metamask-mobile/app/components/Views/Browser/MaxBrowserTabsModal.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/AddNewAccount/AddNewAccountBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissions.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnect.tsx, repos/metamask-mobile/app/components/Views/AccountActions/AccountActions.tsx, repos/metamask-mobile/app/components/UI/WhatsNewModal/WhatsNewModal.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/SkipAccountSecurityModal/index.js, repos/metamask-mobile/app/components/UI/SeedphraseModal/index.js, repos/metamask-mobile/app/components/UI/SelectOptionSheet/OptionsSheet.tsx, repos/metamask-mobile/app/components/UI/QRHardware/QRSigningTransactionModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/NetworkManager/index.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/DeprecatedNetworkModal/DeprecatedNetworkModal.tsx, repos/metamask-mobile/app/components/UI/DeleteWalletModal/index.tsx, repos/metamask-mobile/app/components/UI/DeepLinkModal/DeepLinkModal.tsx, repos/metamask-mobile/app/components/Approvals/AddChainApproval/AddChainApproval.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionModal/SDKSessionModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKLoadingModal/SDKLoadingModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKFeedbackModal/SDKFeedbackModal.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKDisconnectModal/SDKDisconnectModal.tsx, repos/metamask-mobile/app/components/Views/Quiz/SRPQuiz/SRPQuiz.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/RpcSelectionModal/RpcSelectionModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/IntroModal/LearnMoreBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/PermittedNetworksInfoSheet/PermittedNetworksInfoSheet.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/ConnectionDetails/ConnectionDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConfirmRevokeAll/AccountPermissionsConfirmRevokeAll.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetailsSheet/TransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenSortBottomSheet/TokenSortBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Notification/ResetNotificationsModal/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Identity/ConfirmTurnOnBackupAndSyncModal/ConfirmTurnOnBackupAndSyncModal.tsx, repos/metamask-mobile/app/components/UI/Earn/LendingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeNetworkSelectorBase.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityModal/BasicFunctionalityModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/confirm/confirm-component.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/AmbiguousAddressSheet/AmbiguousAddressSheet.tsx, repos/metamask-mobile/app/components/Views/Settings/AdvancedSettings/FiatOnTestnetsFriction/FiatOnTestnetsFriction.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/MultichainAccountActions/MultichainAccountActions.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditAccountName/EditAccountName.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenNetworkBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenPriceChangeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokensBottomSheet/TrendingTokenTimeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/PoolStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/GasImpactModal/index.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/EligibilityFailedModal/EligibilityFailedModal.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictUnavailable/PredictUnavailable.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictOrderRetrySheet/PredictOrderRetrySheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGameDetailsFooter/PredictGameAboutSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictFeeBreakdownSheet/PredictFeeBreakdownSheet.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictAddFundsSheet/PredictAddFundsSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsQuoteExpiredModal/PerpsQuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsProviderSelector/PerpsProviderSelectorSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsOrderTypeBottomSheet/PerpsOrderTypeBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsNotificationBottomSheet/PerpsNotificationBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsModifyActionSheet/PerpsModifyActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLimitPriceBottomSheet/PerpsLimitPriceBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsLeverageBottomSheet/PerpsLeverageBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsFlipPositionConfirmSheet/PerpsFlipPositionConfirmSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCrossMarginWarningBottomSheet/PerpsCrossMarginWarningBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsCandlePeriodBottomSheet/PerpsCandlePeriodBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsBottomSheetTooltip/PerpsBottomSheetTooltip.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsAdjustMarginActionSheet/PerpsAdjustMarginActionSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsTooltipView/PerpsTooltipView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderBookView/PerpsOrderBookView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCloseAllPositionsView/PerpsCloseAllPositionsView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsCancelAllOrdersView/PerpsCancelAllOrdersView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsSourcesFooter/MarketInsightsSourcesFooter.tsx, repos/metamask-mobile/app/components/UI/Earn/modals/LendingMaxWithdrawalModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/MaxInputModal/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenList/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/PasswordBottomSheet/PasswordBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/RecurringFeeModal/RecurringFeeModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/ConfirmModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/Onboarding/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AddFundsBottomSheet/AddFundsBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/DefaultSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/RecipientSelectorModal/RecipientSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/QuoteExpiredModal/QuoteExpiredModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/SlippageModal/CustomSlippageModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/MarketClosedBottomSheets/MarketClosedBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BlockaidModal/BlockaidModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkListModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/pay-with-modal/pay-with-modal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/LevelsTab/RewardsClaimBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/TokenNotAvailableModal/TokenNotAvailableModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/UnsupportedTokenModal/UnsupportedTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/ProviderPickerModal/ProviderPickerModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/SettingsModal/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/FiatSelectorModal/FiatSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Quotes/Quotes.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Checkout/Checkout.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/TronStakingLearnMoreModal/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/WebviewModal/WebviewModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedRegionModal/UnsupportedRegionModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/UnsupportedStateModal/UnsupportedStateModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/SsnInfoModal/SsnInfoModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/TokenSelectorModal/TokenSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/RegionSelectorModal/RegionSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/PaymentMethodSelectorModal/PaymentMethodSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/IncompatibleAccountTokenModal/IncompatibleAccountTokenModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/StateSelectorModal/StateSelectorModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/Modals/Settings/SettingsModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ConfigurationModal/ConfigurationModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/Modals/ErrorDetailsModal/ErrorDetailsModal.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Notification/NotificationMenuItem/Icon.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
-  </si>
-  <si>
-    <t>Badge</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/index.js, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Name/Name.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionListItem/MultichainTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/MultichainBridgeTransactionListItem/MultichainBridgeTransactionListItem.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Base/RemoteImage/RemoteImageBadgeWrapper.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/DetectedTokens/components/Token.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenButton.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-icon/token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-nft/hero-nft.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Headers/NFTImageHeader.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AssetField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NFTCollectionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Trending/components/TrendingTokenRowItem/TrendingTokenRowItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBalance.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderView/PerpsPayRow.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnWithdrawalTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnDepositTokenListItem/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingWithdrawalConfirmationView/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/CardAssetItem/CardAssetItem.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/BlockExplorersModal.tsx, repos/metamask-mobile/app/components/Views/confirmations/legacy/components/AddressElement/AddressElement.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/TokenValueStack/TokenValueStack.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/ActivityEventRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/OrderListItem/OrderListItem.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/Views/confirmations/external/staking/components/staking-contract-interaction-details/staking-contract-interaction-details.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx</t>
-  </si>
-  <si>
-    <t>Avatar</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUIAccountSelector/SnapUIAccountSelector.tsx, repos/metamask-mobile/app/components/UI/WalletAction/WalletAction.tsx, repos/metamask-mobile/app/components/UI/SRPListItem/SRPListItem.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/NetworkInfo/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/NetworkImages/index.tsx, repos/metamask-mobile/app/components/UI/ContextualNetworkPicker/ContextualNetworkPicker.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/NetworkPermissionsConnected/NetworkPermissionsConnected.tsx, repos/metamask-mobile/app/components/Views/AccountPermissions/AccountPermissionsConnected/AccountPermissionsConnected.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/TransactionElement/TransactionDetails/index.js, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Tabs/TabThumbnail/TabThumbnail.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/AvatarGroup.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/Settings/Contacts/ContactForm/index.js, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/TransactionField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/SwapsRateField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/AddressField.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Fields/NetworkFeeField.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AccountSelector.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/switch-account-type-modal.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/AccountInfo/AccountInfo.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/YouReceiveCard/YouReceiveCard.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/ContractTag/ContractTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountTag/AccountTag.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingConfirmation/AccountCard/AccountCard.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/AccountSelector/AccountSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/SendTransaction/SendTransaction.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/account-network-info-row/account-network-info-collapsed/account-network-info-collapsed.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/switch-account-type-modal/account-network-row/account-network-row.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/info-row/info-value/network/network.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiPositionsListItem.tsx, repos/metamask-mobile/app/components/UI/AccountNetworkIndicator/AccountNetworkIndicator.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountsConnectedList/AccountsConnectedList.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/predict-confirmations/predict-claim-footer/predict-claim-footer.tsx</t>
-  </si>
-  <si>
-    <t>Banner</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIBanner/SnapUIBanner.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/NetworkVerificationInfo/NetworkVerificationInfo.tsx, repos/metamask-mobile/app/components/UI/CollectibleDetectionModal/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/PrivateKeyList/PrivateKeyList.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/components/IpfsBanner/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnMaintenanceBanner/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnWithdrawInputView/UnstakeBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/send/recipient/recipient.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/ProtectYourWallet/ProtectYourWallet.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/ClaimBanner/ClaimBanner.tsx, repos/metamask-mobile/app/components/UI/Stake/components/StakingBalance/StakingBanners/UnstakeBanner/UnstakeBanner.tsx</t>
-  </si>
-  <si>
-    <t>Accordion</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-alert-content/blockaid-alert-content.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx</t>
-  </si>
-  <si>
     <t>AccountListHeader</t>
   </si>
   <si>
@@ -608,58 +608,58 @@
     <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
   </si>
   <si>
+    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
+  </si>
+  <si>
     <t>repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/Snaps/SnapUISelector/SnapUISelector.tsx, repos/metamask-mobile/app/components/UI/shared/BaseControlBar/BaseControlBar.tsx, repos/metamask-mobile/app/components/UI/Stake/components/QuickAmounts.tsx, repos/metamask-mobile/app/components/UI/Earn/components/CurrencySwitch.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictGTMModal/PredictGTMModal.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsMarketSortFieldBottomSheet/PerpsMarketSortFieldBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Perps/components/PerpsGTMModal/PerpsGTMModal.tsx, repos/metamask-mobile/app/components/UI/Card/Views/CardWelcome/CardWelcome.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/ResourceToggle/ResourceToggle.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Tron/ResourceToggle/ResourceToggle.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountGroupDetails/AccountGroupDetails.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectCreateInitialAccount/AccountConnectCreateInitialAccount.tsx, repos/metamask-mobile/app/components/Views/AccountConnect/AccountConnectMultiSelector/AccountConnectMultiSelector.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/AboutAsset/ContentDisplay.tsx, repos/metamask-mobile/app/components/Views/confirmations/hooks/alerts/usePendingTransactionAlert.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/index.js, repos/metamask-mobile/app/components/Views/MultichainAccounts/WalletDetails/BaseWalletDetails/index.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/RevealSRP/RevealSRP.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/EditMultichainAccountName/EditMultichainAccountName.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/modals/confirm-alert-modal/confirm-alert-modal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/components/SmartAccountModal/SmartAccountModal.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/AccountDetails/AccountTypes/BaseAccountDetails/index.tsx</t>
-  </si>
-  <si>
     <t>BottomSheetDialog</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/UI/Bridge/components/SwapsKeypad/index.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
+    <t>BannerBase</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx</t>
+  </si>
+  <si>
+    <t>BannerAlert</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/Wallet/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alert-banner/alert-banner.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
+  </si>
+  <si>
+    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAvatar/SnapUIAvatar.tsx, repos/metamask-mobile/app/components/UI/Identicon/index.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx</t>
   </si>
   <si>
     <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/ProgressStepper/index.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/UI/SimulationDetails/AssetPill/AssetPill.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/NetworkRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenNetworkFilterBar/TokenNetworkFilterBar.tsx, repos/metamask-mobile/app/components/Views/Settings/NetworksSettings/NetworkSettings/CustomNetworkView/CustomNetwork.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterSelector/NetworksFilterSelector.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/NetworksFilterBar/NetworksFilterBar.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/rows/transactions/network-row/network-row.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/info/typed-sign-v3v4/info-section-origin-and-details/info-section-origin-and-details.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/OverviewTab/WaysToEarn/SwapSupportedNetworksSection.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapIcon/SnapIcon.tsx, repos/metamask-mobile/app/components/Snaps/SnapAvatar/SnapAvatar.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAssetSelector/SnapUIAssetSelector.tsx, repos/metamask-mobile/app/components/UI/PermissionsSummary/PermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Navbar/index.js, repos/metamask-mobile/app/components/UI/DeFiPositions/DeFiAvatarWithBadge.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionAccountListItem.tsx, repos/metamask-mobile/app/components/Views/SDK/SDKSessionsManager/SDKSessionItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TokenSelectorItem.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/Balance/Balance.tsx, repos/metamask-mobile/app/components/Views/Notifications/Details/Badge/index.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/TokenListItem/TokenListItem.tsx, repos/metamask-mobile/app/components/UI/Predict/components/PredictBalance/PredictBalance.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsWithdrawView/PerpsWithdrawView.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/Views/MarketInsightsView/MarketInsightsView.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnTokenSelector/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnNetworkAvatar/index.tsx, repos/metamask-mobile/app/components/UI/Earn/components/EarnLendingBalance/index.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Card/components/AssetSelectionBottomSheet/AssetSelectionBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Bridge/components/TransactionDetails/TransactionAsset.tsx, repos/metamask-mobile/app/components/UI/Assets/components/AssetLogo/AssetLogo.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/hero-token/avatar-token-with-network-badge/avatar-token-with-network-badge.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/gas/gas-fee-token-icon/gas-fee-token-icon.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/components/PopularTokenRow.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/DepositOrderContent/DepositOrderContent.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Earn/components/Musd/MusdConversionAssetListCta/index.tsx, repos/metamask-mobile/app/components/UI/Card/Views/SpendingLimit/components/AssetCard.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/Erc20TokenHero/index.tsx, repos/metamask-mobile/app/components/UI/Earn/Views/EarnLendingDepositConfirmationView/components/DepositReceiveSection/index.tsx</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Snaps/SnapUIAvatar/SnapUIAvatar.tsx, repos/metamask-mobile/app/components/UI/Identicon/index.tsx, repos/metamask-mobile/app/components/UI/AccountRightButton/index.tsx, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/Views/Settings/GeneralSettings/index.js, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/ActivityTab/EventDetails/GenericEventDetails.tsx</t>
-  </si>
-  <si>
-    <t>BannerBase</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/UI/NetworkConnectionBanner/NetworkConnectionBanner.tsx</t>
-  </si>
-  <si>
-    <t>BannerAlert</t>
-  </si>
-  <si>
-    <t>repos/metamask-mobile/app/components/Views/Wallet/index.tsx, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/Views/ErrorBoundary/index.js, repos/metamask-mobile/app/components/UI/AccountApproval/showWarningBanner.tsx, repos/metamask-mobile/app/components/Views/Snaps/KeyringSnapRemovalWarning/KeyringSnapRemovalWarning.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/blockaid-banner/BlockaidBanner.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/alert-banner/alert-banner.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/DeleteAccount/DeleteAccount.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/BasicInfo.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Bridge/Views/BridgeView/index.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/Modals/PaymentSelectionModal/PaymentSelectionAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/SdkErrorAlert/SdkErrorAlert.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/components/TruncatedError/TruncatedError.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/EnterAddress/EnterAddress.tsx, repos/metamask-mobile/app/components/UI/Ramp/Deposit/Views/BasicInfo/BasicInfo.tsx</t>
-  </si>
-  <si>
     <t>repos/metamask-mobile/app/components/UI/Bridge/components/BridgeTokenSelector/NetworkPills.tsx</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx</t>
+    <t>repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/AssetSelectorButton.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/token/token.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/nft/nft.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-asset/highlighted-asset.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/UI/highlighted-action/highlighted-action.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/Views/BuildQuote/BuildQuote.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/TokenSelectModal/TokenSelectModal.tsx</t>
   </si>
   <si>
     <t>BadgeCount</t>
@@ -689,10 +689,10 @@
     <t>Box</t>
   </si>
   <si>
-    <t>repos/metamask-mobile/app/components/Views/TrendingView/sections.config.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/TrendingView/TrendingView.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/QRAccountDisplay/QRAccountDisplay.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/Pna25BottomSheet/Pna25BottomSheet.tsx, repos/metamask-mobile/app/components/Views/NftFullView/NftFullView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/NetworksManagementView.tsx, repos/metamask-mobile/app/components/Views/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/Homepage/Homepage.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/FeatureFlagOverride/FeatureFlagOverride.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/BrowserTab/BrowserTab.tsx, repos/metamask-mobile/app/components/Views/AddressSelector/AddressSelector.tsx, repos/metamask-mobile/app/components/Views/ActivityView/index.js, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Views/AccountsMenu/AccountsMenu.tsx, repos/metamask-mobile/app/components/Snaps/SnapUIDateTimePicker/SnapUIDateTimePicker.tsx, repos/metamask-mobile/app/components/UI/TurnOffRememberMeModal/TurnOffRememberMeModal.tsx, repos/metamask-mobile/app/components/UI/UrlAutocomplete/Result.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/TransactionElement/ImportWalletTipBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/Tokens/index.tsx, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ReceiveRequest/index.js, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/ProfilerManager/ProfilerManager.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/OTAUpdatesModal/OTAUpdatesModal.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGrid.tsx, repos/metamask-mobile/app/components/UI/NftGrid/NftGridItem.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelectorList/NetworkMultiSelectorList.tsx, repos/metamask-mobile/app/components/UI/NetworkMultiSelector/NetworkMultiSelector.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/MultichainTransactionDetailsModal/MultichainTransactionDetailsSheet.tsx, repos/metamask-mobile/app/components/UI/FundActionMenu/FundActionMenu.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/Carousel/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BrowserBottomBar/index.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.tsx, repos/metamask-mobile/app/components/UI/BalanceEmptyState/BalanceEmptyState.stories.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/components.tsx, repos/metamask-mobile/app/components/Base/Keypad/Keypad.stories.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/EditNetworkMenu.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/DeleteNetworkModal.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/CollapsibleSectionHeader.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/NetworksManagement/components/AdditionalNetworkItem.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainPermissionsSummary/MultichainPermissionsSummary.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountsConnectedList/MultichainAccountsConnectedList.stories.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnect.stories.tsx, repos/metamask-mobile/app/components/UI/shared/ListHeaderWithSearch/ListHeaderWithSearch.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/RemoveTokenBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenList.tsx, repos/metamask-mobile/app/components/UI/TokenDetails/components/MoreTokenActionsMenu.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsDashboard.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsInfoBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsErrorBanner.tsx, repos/metamask-mobile/app/components/UI/Rewards/Views/RewardsSettingsView.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsBottomSheetModal.tsx, repos/metamask-mobile/app/components/UI/Predict/hooks/usePredictToastRegistrations.tsx, repos/metamask-mobile/app/components/UI/Perps/Views/PerpsOrderRedirect.tsx, repos/metamask-mobile/app/components/UI/OnboardingAnimation/__mocks__/OnboardingAnimation.tsx, repos/metamask-mobile/app/components/UI/Notification/List/index.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/MarketInsights/components/MarketInsightsTrendSourcesBottomSheet.tsx, repos/metamask-mobile/app/components/UI/FoxAnimation/__mocks__/FoxAnimation.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCard/StackCard.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Carousel/StackCardEmpty/StackCardEmpty.tsx, repos/metamask-mobile/app/components/UI/Card/routes/OnboardingNavigator.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/BasicFunctionality/BasicFunctionalityEmptyState/BasicFunctionalityEmptyState.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/TronEnergyBandwidthDetail.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/UI/AssetOverview/TronEnergyBandwidthDetail/ResourceRing.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/token-list/token-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-list/recipient-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/recipient-input/recipient-input.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/nft-list/nft-list.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/confirmations/components/network-filter/network-filter.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/SectionHeader/SectionHeader.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/QuickActions/QuickActions.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptySearchResultState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchResults/ExploreSearchResults.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/EmptyErrorState/EmptyErrorTrendingState.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/components/ExploreSearchBar/ExploreSearchBar.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/TrendingView/Views/ExploreSearchScreen/ExploreSearchScreen.tsx, repos/metamask-mobile/app/components/Views/Settings/SecuritySettings/Sections/DeviceSecurityToggle.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddressQR/ShareAddressQR.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/sheets/ShareAddress/ShareAddress.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionRow/SectionRow.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionTitle/SectionTitle.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/ErrorState/ErrorState.tsx, repos/metamask-mobile/app/components/Views/Homepage/components/SectionCard/SectionCard.tsx, repos/metamask-mobile/app/components/Views/MultichainAccounts/MultichainAccountConnect/MultichainAccountConnectMultiSelector/MultichainAccountConnectMultiSelector.stories.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Perps/PerpsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Predictions/PredictionsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/Tokens/TokensSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/DeFi/DeFiSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/Homepage/Sections/NFTs/NFTsSection.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenAutoComplete/SearchTokenAutocomplete.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkSelector/NetworkSelector.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/SearchTokenResults/SearchTokenResults.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/NetworkListBottomSheet/NetworkListBottomSheet.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomCollectible/AddCustomCollectible.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/components/AddCustomToken/AddCustomToken.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/NFTView/NFTView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/ConfirmAddTokenView/ConfirmAddAsset.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/Views/AddAsset/Views/TokenView/TokenView.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Tokens/TokenList/TokenListItemV2/TokenListItemV2.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SitesSearchFooter/SitesSearchFooter.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Sites/components/SiteRowItem/SiteRowItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ThemeImageComponent/RewardsThemeImageComponent.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/UpcomingSnapshotTileCondensed.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroupList.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardSettingsAccountGroup.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SnapshotTile/SnapshotTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/ReferredByCodeSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/RewardOptInAccountGroupModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Settings/NetworkAvatars.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Tabs/RewardsActivity.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/SeasonStatus/SeasonStatus.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardsImageModal/RewardsImageModal.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/RewardItem/RewardItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralActionsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralInfoSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/ReferralStatsSection.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/ReferralDetails/CopyableField.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummaryTile.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonUnlockedRewards.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonReferralDetails.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonSummary.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonLevel.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/PreviousSeason/PreviousSeasonBalance.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/RewardsLegalDisclaimer.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep1.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep3.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep2.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/ProgressIndicator.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/EndOfSeasonClaimBottomSheet/EndOfSeasonClaimBottomSheet.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingIntroStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingStep4.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/NativeFlow/OtpCode.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/AccountDisplayItem/AccountDisplayItem.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Rewards/components/Onboarding/OnboardingNoActiveSeasonStep.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/Views/TokenSelection/TokenSelection.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/components/RampUnsupportedModal/RampUnsupportedModal.tsx, repos/metamask-mobile/app/components/UI/Ramp/Aggregator/components/DownChevronText.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTransactionsView.tsx, repos/metamask-mobile/app/components/UI/Predict/views/PredictTransactionsView/PredictTr